--- a/src/test/resources/excel_data/Data_for_project.xlsx
+++ b/src/test/resources/excel_data/Data_for_project.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bhavanakandula/eclipse-workspace/Parallel-testing/src/test/resources/excel_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1AA787-DF96-F042-A2E2-D1875C0A814F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE1F663B-FBB1-AA41-AB5D-F146F5C22A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16940" xr2:uid="{AF27C5E6-52B6-B843-B9F8-F5B35314C0ED}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -73,6 +73,13 @@
     </font>
     <font>
       <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="10"/>
       <name val="Aptos Narrow"/>
@@ -101,9 +108,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -448,22 +456,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -471,15 +479,17 @@
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>12345687</v>
       </c>
+      <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>2341234</v>
       </c>
+      <c r="F2" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
